--- a/StateOfPractice/DomainMeasurements/InverseKinematics-Ryan/appendix-B-wide-summary.xlsx
+++ b/StateOfPractice/DomainMeasurements/InverseKinematics-Ryan/appendix-B-wide-summary.xlsx
@@ -1,25 +1,40 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\coding\AIMSS\StateOfPractice\DomainMeasurements\InverseKinematics-Ryan\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C5ED504A-D265-4BBC-90A2-1D4A6FA34461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{13EACBBB-515C-4578-B0CD-15DF7D604EB9}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="appendix-B-wide-summary" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="0"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel</Application>
+  <DocSecurity>0</DocSecurity>
+  <ScaleCrop>false</ScaleCrop>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>工作表</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>1</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="1" baseType="lpstr">
+      <vt:lpstr>appendix-B-wide-summary</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+  <LinksUpToDate>false</LinksUpToDate>
+  <SharedDoc>false</SharedDoc>
+  <HyperlinksChanged>false</HyperlinksChanged>
+  <AppVersion>16.0300</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <cp:lastModifiedBy>Ziyang Fang</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-04-05T21:58:33Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-04-05T22:02:34Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2303" uniqueCount="757">
   <si>
     <t>Metric</t>
@@ -2297,7 +2312,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -2953,7 +2968,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -3268,7 +3283,27 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\coding\AIMSS\StateOfPractice\DomainMeasurements\InverseKinematics-Ryan\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C5ED504A-D265-4BBC-90A2-1D4A6FA34461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{13EACBBB-515C-4578-B0CD-15DF7D604EB9}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="appendix-B-wide-summary" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="0"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A435A6A8-4625-45DB-B221-D541C0332490}">
   <dimension ref="A1:AD109"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
@@ -3911,8 +3946,10 @@
       <c r="A8" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B8" s="2">
-        <v>41014</v>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2012-04-15</t>
+        </is>
       </c>
       <c r="C8" s="2">
         <v>1996</v>
@@ -4089,11 +4126,15 @@
       <c r="A10" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>154</v>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alive</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alive</t>
+        </is>
       </c>
       <c r="D10" s="1" t="s">
         <v>155</v>
@@ -4899,11 +4940,15 @@
       <c r="A19" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>235</v>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Development began in 2002 at USC. Gazebo Classic (original version) reached EOL January 2025. Current version is Gazebo (formerly Ignition), representing over 16 years of development. Latest release: Jetty (September 2025, LTS version). Maintainer: arjoc@intrinsic.ai</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Development began in 1996 at EPFL by Dr. Olivier Michel. Commercialized by Cyberbotics Ltd. since 1998. Became free and open-source in December 2018. Over 250,000 downloads since open-sourcing. Beginner-friendly software for robotics education and research.</t>
+        </is>
       </c>
       <c r="D19" s="1" t="s">
         <v>236</v>
@@ -4989,11 +5034,15 @@
       <c r="A20" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>263</v>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
       </c>
       <c r="D20" s="1" t="s">
         <v>232</v>
@@ -6339,11 +6388,16 @@
       <c r="A35" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>290</v>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+          </t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Desktop package installation is straightforward on Linux; validation via bundled demo worlds is simple.</t>
+        </is>
       </c>
       <c r="D35" s="1" t="s">
         <v>291</v>
@@ -7239,11 +7293,16 @@
       <c r="A45" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>344</v>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+          </t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tutorial behavior is reproducible for default examples and reference controllers.</t>
+        </is>
       </c>
       <c r="D45" s="1" t="s">
         <v>345</v>
@@ -7869,11 +7928,15 @@
       <c r="A52" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>377</v>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No major instability observed during install and initial tutorial execution.</t>
+        </is>
       </c>
       <c r="D52" s="1" t="s">
         <v>378</v>
@@ -8229,11 +8292,16 @@
       <c r="A56" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>407</v>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+          </t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error reporting is generally clear for invalid world files and missing assets.</t>
+        </is>
       </c>
       <c r="D56" s="1" t="s">
         <v>408</v>
@@ -8769,11 +8837,15 @@
       <c r="A62" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>466</v>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Good documentation and examples; still assumes basic robotics simulation knowledge.</t>
+        </is>
       </c>
       <c r="D62" s="1" t="s">
         <v>467</v>
@@ -8919,8 +8991,10 @@
       <c r="U63" s="1">
         <v>2.9</v>
       </c>
-      <c r="V63" s="1">
-        <v>4</v>
+      <c r="V63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.0</t>
+        </is>
       </c>
       <c r="W63" s="1">
         <v>0.3</v>
@@ -8928,8 +9002,10 @@
       <c r="X63" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="Y63" s="1">
-        <v>1</v>
+      <c r="Y63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.0</t>
+        </is>
       </c>
       <c r="Z63" s="1">
         <v>2.12</v>
@@ -9277,8 +9353,10 @@
       <c r="U67" s="1">
         <v>0.73</v>
       </c>
-      <c r="V67" s="1">
-        <v>0.45</v>
+      <c r="V67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45%</t>
+        </is>
       </c>
       <c r="W67" s="1">
         <v>0.71</v>
@@ -9286,8 +9364,10 @@
       <c r="X67" s="1">
         <v>0.68</v>
       </c>
-      <c r="Y67" s="1">
-        <v>0.4</v>
+      <c r="Y67" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40%</t>
+        </is>
       </c>
       <c r="Z67" s="1">
         <v>0.8</v>
@@ -9310,8 +9390,10 @@
       <c r="B68" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="C68" s="1">
-        <v>0.14000000000000001</v>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14%</t>
+        </is>
       </c>
       <c r="D68" s="1">
         <v>0.11</v>
@@ -9367,8 +9449,10 @@
       <c r="U68" s="1">
         <v>0.14000000000000001</v>
       </c>
-      <c r="V68" s="1">
-        <v>0.11</v>
+      <c r="V68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11%</t>
+        </is>
       </c>
       <c r="W68" s="1">
         <v>0.14000000000000001</v>
@@ -9376,8 +9460,10 @@
       <c r="X68" s="1">
         <v>0.13</v>
       </c>
-      <c r="Y68" s="1">
-        <v>0.1</v>
+      <c r="Y68" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10%</t>
+        </is>
       </c>
       <c r="Z68" s="1">
         <v>0.16</v>
@@ -9580,8 +9666,10 @@
       <c r="B71" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>529</v>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Active development with 15,731 commits. Community contributions welcome in bug reporting, documentation, translations, Python/C/C++ programming, and 3D modeling.</t>
+        </is>
       </c>
       <c r="D71" s="1" t="s">
         <v>530</v>
@@ -9667,8 +9755,11 @@
       <c r="A72" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>557</v>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+          </t>
+        </is>
       </c>
       <c r="C72" s="1">
         <v>8</v>
@@ -9937,11 +10028,16 @@
       <c r="A75" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>559</v>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+          </t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supports multiple programming languages (C, C++, Python, Java, MATLAB). Provides APIs for robot control and sensor access. Pre-built robot models and environments available.</t>
+        </is>
       </c>
       <c r="D75" s="1" t="s">
         <v>560</v>
@@ -10837,11 +10933,16 @@
       <c r="A85" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>596</v>
+      <c r="B85" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+          </t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Code organization is generally clear, with some legacy modules less documented.</t>
+        </is>
       </c>
       <c r="D85" s="1" t="s">
         <v>597</v>
@@ -11377,11 +11478,16 @@
       <c r="A91" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>629</v>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+          </t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transparent open-source development with active community involvement</t>
+        </is>
       </c>
       <c r="D91" s="1" t="s">
         <v>630</v>
@@ -11920,8 +12026,10 @@
       <c r="B97" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="C97" s="1">
-        <v>15731</v>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15,731</t>
+        </is>
       </c>
       <c r="D97" s="1">
         <v>4823</v>
@@ -12706,8 +12814,10 @@
       <c r="X105" s="1">
         <v>2300</v>
       </c>
-      <c r="Y105" s="1">
-        <v>1300</v>
+      <c r="Y105" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1,300</t>
+        </is>
       </c>
       <c r="Z105" s="1">
         <v>1100</v>
